--- a/data/WORDPROC/Resultados/nrp50 alumnos.xlsx
+++ b/data/WORDPROC/Resultados/nrp50 alumnos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imagu\ANRPDecisionSpace\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imagu\ANRPDecisionSpace\data\WORDPROC\Resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja3" sheetId="3" r:id="rId2"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913" concurrentCalc="0"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="276">
   <si>
     <t>ID</t>
   </si>
@@ -823,7 +823,37 @@
     <t>Coupling</t>
   </si>
   <si>
-    <t>+A3+A2:E+A2:E12</t>
+    <t>Se mapea con</t>
+  </si>
+  <si>
+    <t>Effort</t>
+  </si>
+  <si>
+    <t>effort</t>
+  </si>
+  <si>
+    <t>'Open+Save(+SaveAs)</t>
+  </si>
+  <si>
+    <t>Cut+Copy+Paste</t>
+  </si>
+  <si>
+    <t>Header/Footer/PageNumber</t>
+  </si>
+  <si>
+    <t>Help + Seach</t>
+  </si>
+  <si>
+    <t>Table functions</t>
+  </si>
+  <si>
+    <t>requiremetn level up</t>
+  </si>
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t>Name coupled</t>
   </si>
 </sst>
 </file>
@@ -947,7 +977,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -1078,6 +1108,22 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1134,7 +1180,7 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Hoja2!$T$2:$T$51</c:f>
+              <c:f>Hoja2!$R$2:$R$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -1315,7 +1361,7 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Hoja2!$U$2:$U$51</c:f>
+              <c:f>Hoja2!$S$2:$S$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -1496,7 +1542,7 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Hoja2!$V$2:$V$51</c:f>
+              <c:f>Hoja2!$T$2:$T$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -1677,7 +1723,7 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Hoja2!$W$2:$W$51</c:f>
+              <c:f>Hoja2!$U$2:$U$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -2585,13 +2631,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
       <xdr:row>73</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
@@ -4188,317 +4234,333 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD51"/>
+  <dimension ref="A1:AF51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="6" max="6" width="31.84375" customWidth="1"/>
-    <col min="7" max="7" width="10.15234375" style="13" customWidth="1"/>
-    <col min="8" max="19" width="5.3828125" customWidth="1"/>
+    <col min="4" max="4" width="31.84375" customWidth="1"/>
+    <col min="5" max="5" width="10.15234375" style="13" customWidth="1"/>
+    <col min="6" max="17" width="5.3828125" customWidth="1"/>
+    <col min="29" max="29" width="11.07421875" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="24.9" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" spans="1:32" ht="24.9" x14ac:dyDescent="0.4">
+      <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="F1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="R1" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="S1" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="T1" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="U1" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="X1" t="s">
+        <v>267</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB1" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="11"/>
-      <c r="H1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="I1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J1" t="s">
-        <v>154</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="T1" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="U1" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="V1" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="W1" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="Y1" s="7" t="s">
+      <c r="AC1" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="AD1" s="36"/>
+      <c r="AE1" t="s">
+        <v>265</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="12">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1</v>
+      </c>
+      <c r="J2" s="4">
+        <v>1</v>
+      </c>
+      <c r="K2" s="4">
+        <v>1</v>
+      </c>
+      <c r="L2" s="4">
+        <v>1</v>
+      </c>
+      <c r="M2" s="4">
+        <v>1</v>
+      </c>
+      <c r="N2" s="4">
+        <v>1</v>
+      </c>
+      <c r="O2" s="4">
+        <v>1</v>
+      </c>
+      <c r="P2" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>2</v>
+      </c>
+      <c r="R2">
+        <f>COUNTIF(F2:Q2,1)</f>
+        <v>11</v>
+      </c>
+      <c r="S2">
+        <f>COUNTIF(F2:Q2,2)</f>
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <f>COUNTIF(F2:Q2,3)</f>
         <v>0</v>
       </c>
-      <c r="Z1" s="7"/>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="7"/>
-      <c r="AC1" s="7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" ht="25.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="17" t="s">
+      <c r="U2">
+        <f>COUNTIF(F2:Q2,4)</f>
+        <v>0</v>
+      </c>
+      <c r="V2" s="12">
+        <v>1</v>
+      </c>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12">
+        <v>66</v>
+      </c>
+      <c r="Y2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z2" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="AA2" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="AB2" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G2" s="12">
-        <v>1</v>
-      </c>
-      <c r="H2" s="4">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2" s="4">
-        <v>1</v>
-      </c>
-      <c r="L2" s="4">
-        <v>1</v>
-      </c>
-      <c r="M2" s="4">
-        <v>1</v>
-      </c>
-      <c r="N2" s="4">
-        <v>1</v>
-      </c>
-      <c r="O2" s="4">
-        <v>1</v>
-      </c>
-      <c r="P2" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>1</v>
-      </c>
-      <c r="R2" s="4">
-        <v>1</v>
-      </c>
-      <c r="S2" s="4">
-        <v>2</v>
-      </c>
-      <c r="T2">
-        <f>COUNTIF(H2:S2,1)</f>
+      <c r="AC2" s="5" t="str">
+        <f>+Z2</f>
+        <v>New File</v>
+      </c>
+      <c r="AD2" s="5"/>
+      <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" ht="38.15" x14ac:dyDescent="0.4">
+      <c r="A3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="12">
+        <f>+E2+1</f>
+        <v>2</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1</v>
+      </c>
+      <c r="J3" s="4">
+        <v>1</v>
+      </c>
+      <c r="K3" s="4">
+        <v>1</v>
+      </c>
+      <c r="L3" s="4">
+        <v>2</v>
+      </c>
+      <c r="M3" s="4">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1</v>
+      </c>
+      <c r="O3" s="4">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R51" si="0">COUNTIF(F3:Q3,1)</f>
         <v>11</v>
       </c>
-      <c r="U2">
-        <f>COUNTIF(H2:S2,2)</f>
-        <v>1</v>
-      </c>
-      <c r="V2">
-        <f>COUNTIF(H2:S2,3)</f>
+      <c r="S3">
+        <f t="shared" ref="S3:S51" si="1">COUNTIF(F3:Q3,2)</f>
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T51" si="2">COUNTIF(F3:Q3,3)</f>
         <v>0</v>
       </c>
-      <c r="W2">
-        <f>COUNTIF(H2:S2,4)</f>
+      <c r="U3">
+        <f t="shared" ref="U3:U51" si="3">COUNTIF(F3:Q3,4)</f>
         <v>0</v>
       </c>
-      <c r="X2" s="12">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="Z2" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA2" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB2" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="AC2" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="AD2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" ht="38.15" x14ac:dyDescent="0.4">
-      <c r="A3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="17" t="s">
+      <c r="V3" s="12">
+        <f>+V2+1</f>
+        <v>2</v>
+      </c>
+      <c r="W3" s="12"/>
+      <c r="X3" s="12">
+        <v>76</v>
+      </c>
+      <c r="Y3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z3" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="AA3" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="AB3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="12">
-        <f>+G2+1</f>
-        <v>2</v>
-      </c>
-      <c r="H3" s="4">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" s="4">
-        <v>1</v>
-      </c>
-      <c r="L3" s="4">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4">
-        <v>1</v>
-      </c>
-      <c r="N3" s="4">
-        <v>2</v>
-      </c>
-      <c r="O3" s="4">
-        <v>1</v>
-      </c>
-      <c r="P3" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>1</v>
-      </c>
-      <c r="R3" s="4">
-        <v>1</v>
-      </c>
-      <c r="S3" s="4">
-        <v>1</v>
-      </c>
-      <c r="T3">
-        <f t="shared" ref="T3:T51" si="0">COUNTIF(H3:S3,1)</f>
-        <v>11</v>
-      </c>
-      <c r="U3">
-        <f t="shared" ref="U3:U51" si="1">COUNTIF(H3:S3,2)</f>
-        <v>1</v>
-      </c>
-      <c r="V3">
-        <f t="shared" ref="V3:V51" si="2">COUNTIF(H3:S3,3)</f>
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <f t="shared" ref="W3:W51" si="3">COUNTIF(H3:S3,4)</f>
-        <v>0</v>
-      </c>
-      <c r="X3" s="12">
-        <f>+X2+1</f>
-        <v>2</v>
-      </c>
-      <c r="Y3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z3" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA3" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="AB3" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="AC3" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" ht="38.15" x14ac:dyDescent="0.4">
-      <c r="A4" s="8" t="s">
+      <c r="AC3" s="39" t="s">
+        <v>268</v>
+      </c>
+      <c r="AD3" s="37"/>
+      <c r="AE3">
+        <v>2</v>
+      </c>
+      <c r="AF3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" ht="38.15" x14ac:dyDescent="0.4">
+      <c r="A4" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="17" t="s">
+      <c r="B4" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="C4" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="E4" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G4" s="12">
-        <f t="shared" ref="G4:G51" si="4">+G3+1</f>
-        <v>3</v>
-      </c>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
+      <c r="E4" s="12">
+        <f t="shared" ref="E4:E51" si="4">+E3+1</f>
+        <v>3</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4">
+        <v>2</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
       </c>
       <c r="L4" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="4">
         <v>1</v>
@@ -4515,81 +4577,84 @@
       <c r="Q4" s="4">
         <v>1</v>
       </c>
-      <c r="R4" s="4">
-        <v>1</v>
-      </c>
-      <c r="S4" s="4">
-        <v>1</v>
-      </c>
-      <c r="T4">
+      <c r="R4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="S4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="U4">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="V4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="W4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="V4" s="12">
+        <f t="shared" ref="V4:V51" si="5">+V3+1</f>
+        <v>3</v>
+      </c>
+      <c r="W4" s="12"/>
       <c r="X4" s="12">
-        <f t="shared" ref="X4:X51" si="5">+X3+1</f>
-        <v>3</v>
-      </c>
-      <c r="Y4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y4" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="Z4" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA4" s="17" t="s">
+      <c r="Z4" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="AB4" s="20" t="s">
+      <c r="AA4" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="AC4" s="17" t="s">
+      <c r="AB4" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" ht="25.75" x14ac:dyDescent="0.4">
-      <c r="A5" s="8" t="s">
+      <c r="AC4" s="37" t="str">
+        <f>+Z4</f>
+        <v>Close File</v>
+      </c>
+      <c r="AD4" s="37"/>
+      <c r="AE4">
+        <v>3</v>
+      </c>
+      <c r="AF4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="17" t="s">
+      <c r="B5" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="C5" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="E5" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G5" s="12">
+      <c r="E5" s="12">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="H5" s="4">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4">
         <v>1</v>
       </c>
       <c r="K5" s="4">
@@ -4613,85 +4678,82 @@
       <c r="Q5" s="4">
         <v>1</v>
       </c>
-      <c r="R5" s="4">
-        <v>1</v>
-      </c>
-      <c r="S5" s="4">
-        <v>1</v>
-      </c>
-      <c r="T5">
+      <c r="R5">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="U5">
+      <c r="S5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V5">
+      <c r="T5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W5">
+      <c r="U5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="V5" s="12">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="W5" s="12"/>
       <c r="X5" s="12">
-        <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="Y5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="Z5" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA5" s="17" t="s">
+      <c r="Z5" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="AB5" s="20" t="s">
+      <c r="AA5" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="AC5" s="17" t="s">
+      <c r="AB5" s="17" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:30" ht="50.6" x14ac:dyDescent="0.4">
-      <c r="A6" s="8" t="s">
+      <c r="AC5" s="40"/>
+      <c r="AD5" s="37"/>
+    </row>
+    <row r="6" spans="1:32" ht="50.6" x14ac:dyDescent="0.4">
+      <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="17" t="s">
+      <c r="B6" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="C6" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="E6" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="12">
+      <c r="E6" s="12">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="H6" s="4">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4">
+        <v>2</v>
+      </c>
+      <c r="J6" s="4">
         <v>1</v>
       </c>
       <c r="K6" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" s="4">
         <v>1</v>
@@ -4700,184 +4762,184 @@
         <v>2</v>
       </c>
       <c r="O6" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P6" s="4">
         <v>2</v>
       </c>
       <c r="Q6" s="4">
-        <v>4</v>
-      </c>
-      <c r="R6" s="4">
-        <v>2</v>
-      </c>
-      <c r="S6" s="4">
-        <v>2</v>
-      </c>
-      <c r="T6">
+        <v>2</v>
+      </c>
+      <c r="R6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="U6">
+      <c r="S6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="V6">
+      <c r="T6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W6">
+      <c r="U6">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="X6" s="12">
+      <c r="V6" s="12">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="Y6" s="8" t="s">
+      <c r="W6" s="12"/>
+      <c r="X6" s="12">
+        <v>65</v>
+      </c>
+      <c r="Y6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="Z6" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA6" s="17" t="s">
+      <c r="Z6" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="AB6" s="20" t="s">
+      <c r="AA6" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="AC6" s="17" t="s">
+      <c r="AB6" s="17" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="7" spans="1:30" ht="87.9" x14ac:dyDescent="0.4">
-      <c r="A7" s="8" t="s">
+      <c r="AC6" s="40"/>
+      <c r="AD6" s="37"/>
+    </row>
+    <row r="7" spans="1:32" ht="87.9" x14ac:dyDescent="0.4">
+      <c r="A7" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="17" t="s">
+      <c r="B7" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="C7" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="E7" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G7" s="12">
+      <c r="E7" s="12">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="H7" s="4">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
+      <c r="F7" s="4">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7" s="4">
+        <v>3</v>
+      </c>
+      <c r="J7" s="4">
         <v>3</v>
       </c>
       <c r="K7" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M7" s="4">
         <v>2</v>
       </c>
       <c r="N7" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O7" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P7" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q7" s="4">
-        <v>3</v>
-      </c>
-      <c r="R7" s="4">
-        <v>3</v>
-      </c>
-      <c r="S7" s="4">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="T7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="U7">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="V7">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="W7">
+      <c r="U7">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="X7" s="12">
+      <c r="V7" s="12">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="Y7" s="8" t="s">
+      <c r="W7" s="12"/>
+      <c r="X7" s="12">
+        <v>81</v>
+      </c>
+      <c r="Y7" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="Z7" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA7" s="17" t="s">
+      <c r="Z7" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="AB7" s="20" t="s">
+      <c r="AA7" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="AC7" s="17" t="s">
+      <c r="AB7" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" ht="50.6" x14ac:dyDescent="0.4">
-      <c r="A8" s="8" t="s">
+      <c r="AC7" s="37" t="str">
+        <f>+Z7</f>
+        <v>Search File</v>
+      </c>
+      <c r="AD7" s="37"/>
+      <c r="AE7">
+        <v>4</v>
+      </c>
+      <c r="AF7">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="50.6" x14ac:dyDescent="0.4">
+      <c r="A8" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="24" t="s">
+      <c r="B8" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="C8" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="E8" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="12">
+      <c r="E8" s="12">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="H8" s="4">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>3</v>
-      </c>
-      <c r="J8">
+      <c r="F8" s="4">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8" s="4">
+        <v>3</v>
+      </c>
+      <c r="J8" s="4">
         <v>4</v>
       </c>
       <c r="K8" s="4">
@@ -4890,93 +4952,96 @@
         <v>3</v>
       </c>
       <c r="N8" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O8" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P8" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="4">
         <v>4</v>
       </c>
-      <c r="R8" s="4">
-        <v>4</v>
-      </c>
-      <c r="S8" s="4">
-        <v>4</v>
-      </c>
-      <c r="T8">
+      <c r="R8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U8">
+      <c r="S8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V8">
+      <c r="T8">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="W8">
+      <c r="U8">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="X8" s="12">
+      <c r="V8" s="12">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="Y8" s="8" t="s">
+      <c r="W8" s="12"/>
+      <c r="X8" s="12">
+        <v>19</v>
+      </c>
+      <c r="Y8" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="Z8" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA8" s="24" t="s">
+      <c r="Z8" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="AB8" s="20" t="s">
+      <c r="AA8" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="AC8" s="25" t="s">
+      <c r="AB8" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="AD8">
+      <c r="AC8" s="38" t="str">
+        <f>+Z8</f>
+        <v>Protect File</v>
+      </c>
+      <c r="AD8" s="38"/>
+      <c r="AE8">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" ht="38.15" x14ac:dyDescent="0.4">
-      <c r="A9" s="8" t="s">
+      <c r="AF8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" ht="38.15" x14ac:dyDescent="0.4">
+      <c r="A9" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="17" t="s">
+      <c r="B9" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="C9" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="E9" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="12">
+      <c r="E9" s="12">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="H9" s="4">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>3</v>
-      </c>
-      <c r="J9">
-        <v>2</v>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9" s="4">
+        <v>3</v>
+      </c>
+      <c r="J9" s="4">
+        <v>3</v>
       </c>
       <c r="K9" s="4">
         <v>3</v>
@@ -4988,108 +5053,111 @@
         <v>3</v>
       </c>
       <c r="N9" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O9" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P9" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="4">
         <v>2</v>
       </c>
-      <c r="R9" s="4">
-        <v>2</v>
-      </c>
-      <c r="S9" s="4">
-        <v>2</v>
+      <c r="R9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="T9">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="U9">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="V9">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="W9">
+      <c r="U9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X9" s="12">
+      <c r="V9" s="12">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="Y9" s="8" t="s">
+      <c r="W9" s="12"/>
+      <c r="X9" s="12">
+        <v>52</v>
+      </c>
+      <c r="Y9" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="Z9" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA9" s="17" t="s">
+      <c r="Z9" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="AB9" s="20" t="s">
+      <c r="AA9" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="AC9" s="17" t="s">
+      <c r="AB9" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD9">
+      <c r="AC9" s="37" t="str">
+        <f>+Z9</f>
+        <v>Print Preview</v>
+      </c>
+      <c r="AD9" s="37"/>
+      <c r="AE9">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" ht="38.15" x14ac:dyDescent="0.4">
-      <c r="A10" s="8" t="s">
+      <c r="AF9">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" ht="38.15" x14ac:dyDescent="0.4">
+      <c r="A10" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="17" t="s">
+      <c r="B10" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="C10" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="E10" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G10" s="12">
+      <c r="E10" s="12">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="H10" s="4">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>2</v>
-      </c>
-      <c r="J10">
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
+      <c r="J10" s="4">
         <v>1</v>
       </c>
       <c r="K10" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" s="4">
         <v>1</v>
       </c>
       <c r="M10" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" s="4">
         <v>1</v>
       </c>
       <c r="O10" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10" s="4">
         <v>1</v>
@@ -5097,82 +5165,85 @@
       <c r="Q10" s="4">
         <v>2</v>
       </c>
-      <c r="R10" s="4">
-        <v>1</v>
-      </c>
-      <c r="S10" s="4">
-        <v>2</v>
-      </c>
-      <c r="T10">
+      <c r="R10">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="U10">
+      <c r="S10">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="V10">
+      <c r="T10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W10">
+      <c r="U10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X10" s="12">
+      <c r="V10" s="12">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="Y10" s="8" t="s">
+      <c r="W10" s="12"/>
+      <c r="X10" s="12">
+        <v>42</v>
+      </c>
+      <c r="Y10" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="Z10" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA10" s="17" t="s">
+      <c r="Z10" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="AB10" s="20" t="s">
+      <c r="AA10" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="AC10" s="17" t="s">
+      <c r="AB10" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD10">
+      <c r="AC10" s="37" t="str">
+        <f>+Z10</f>
+        <v>Print File</v>
+      </c>
+      <c r="AD10" s="37"/>
+      <c r="AE10">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" ht="50.6" x14ac:dyDescent="0.4">
-      <c r="A11" s="8" t="s">
+      <c r="AF10">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" ht="50.6" x14ac:dyDescent="0.4">
+      <c r="A11" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="17" t="s">
+      <c r="B11" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="C11" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="E11" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G11" s="12">
+      <c r="E11" s="12">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="H11" s="4">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>3</v>
-      </c>
-      <c r="J11">
-        <v>3</v>
+      <c r="F11" s="4">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+      <c r="I11" s="4">
+        <v>3</v>
+      </c>
+      <c r="J11" s="4">
+        <v>4</v>
       </c>
       <c r="K11" s="4">
         <v>3</v>
@@ -5181,206 +5252,212 @@
         <v>4</v>
       </c>
       <c r="M11" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N11" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O11" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P11" s="4">
         <v>2</v>
       </c>
       <c r="Q11" s="4">
-        <v>3</v>
-      </c>
-      <c r="R11" s="4">
-        <v>2</v>
-      </c>
-      <c r="S11" s="4">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="T11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="U11">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="V11">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="W11">
+      <c r="U11">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="X11" s="12">
+      <c r="V11" s="12">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="Y11" s="8" t="s">
+      <c r="W11" s="12"/>
+      <c r="X11" s="12">
+        <v>60</v>
+      </c>
+      <c r="Y11" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="Z11" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA11" s="17" t="s">
+      <c r="Z11" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="AB11" s="20" t="s">
+      <c r="AA11" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="AC11" s="17" t="s">
+      <c r="AB11" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD11">
+      <c r="AC11" s="37" t="str">
+        <f>+Z11</f>
+        <v>Send To</v>
+      </c>
+      <c r="AD11" s="37"/>
+      <c r="AE11">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:30" ht="50.6" x14ac:dyDescent="0.4">
-      <c r="A12" s="8" t="s">
+      <c r="AF11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" ht="50.6" x14ac:dyDescent="0.4">
+      <c r="A12" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="24" t="s">
+      <c r="B12" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="C12" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="E12" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G12" s="12">
+      <c r="E12" s="12">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="H12" s="4">
-        <v>4</v>
-      </c>
-      <c r="I12">
-        <v>2</v>
-      </c>
-      <c r="J12">
-        <v>3</v>
+      <c r="F12" s="4">
+        <v>4</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12" s="4">
+        <v>4</v>
+      </c>
+      <c r="J12" s="4">
+        <v>4</v>
       </c>
       <c r="K12" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L12" s="4">
         <v>4</v>
       </c>
       <c r="M12" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N12" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O12" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P12" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q12" s="4">
-        <v>4</v>
-      </c>
-      <c r="R12" s="4">
-        <v>3</v>
-      </c>
-      <c r="S12" s="4">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="T12">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="U12">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="V12">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="W12">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="X12" s="12">
+      <c r="V12" s="12">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="Y12" s="8" t="s">
+      <c r="W12" s="12"/>
+      <c r="X12" s="12">
+        <v>19</v>
+      </c>
+      <c r="Y12" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="Z12" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA12" s="24" t="s">
+      <c r="Z12" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="AB12" s="20" t="s">
+      <c r="AA12" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="AC12" s="25" t="s">
+      <c r="AB12" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="AD12">
+      <c r="AC12" s="38" t="str">
+        <f>+Z12</f>
+        <v>Set Properties</v>
+      </c>
+      <c r="AD12" s="38"/>
+      <c r="AE12">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" ht="87.9" x14ac:dyDescent="0.4">
-      <c r="A13" s="8" t="s">
+      <c r="AF12">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" ht="87.9" x14ac:dyDescent="0.4">
+      <c r="A13" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="28" t="s">
+      <c r="B13" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="C13" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="E13" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="12">
+      <c r="E13" s="12">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="H13" s="4">
-        <v>1</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4">
+        <v>2</v>
       </c>
       <c r="K13" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="4">
         <v>2</v>
       </c>
       <c r="M13" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" s="4">
         <v>1</v>
@@ -5389,1057 +5466,1077 @@
         <v>1</v>
       </c>
       <c r="Q13" s="4">
-        <v>1</v>
-      </c>
-      <c r="R13" s="4">
-        <v>1</v>
-      </c>
-      <c r="S13" s="4">
-        <v>2</v>
-      </c>
-      <c r="T13">
+        <v>2</v>
+      </c>
+      <c r="R13">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="U13">
+      <c r="S13">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="V13">
+      <c r="T13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W13">
+      <c r="U13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X13" s="12">
+      <c r="V13" s="12">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="Y13" s="8" t="s">
+      <c r="W13" s="12"/>
+      <c r="X13" s="12">
+        <v>12</v>
+      </c>
+      <c r="Y13" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="Z13" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA13" s="28" t="s">
+      <c r="Z13" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="AB13" s="29" t="s">
+      <c r="AA13" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="AC13" s="17" t="s">
+      <c r="AB13" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD13">
+      <c r="AC13" s="37" t="str">
+        <f>+Z13</f>
+        <v>Exit</v>
+      </c>
+      <c r="AD13" s="37"/>
+      <c r="AE13">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" ht="75.45" x14ac:dyDescent="0.4">
-      <c r="A14" s="8" t="s">
+      <c r="AF13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" ht="75.45" x14ac:dyDescent="0.4">
+      <c r="A14" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="17" t="s">
+      <c r="B14" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="C14" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="E14" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="12">
+      <c r="E14" s="12">
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="H14" s="4">
-        <v>1</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" s="4">
+        <v>2</v>
+      </c>
+      <c r="J14" s="4">
+        <v>2</v>
       </c>
       <c r="K14" s="4">
         <v>2</v>
       </c>
       <c r="L14" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M14" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N14" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O14" s="4">
         <v>1</v>
       </c>
       <c r="P14" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="4">
-        <v>1</v>
-      </c>
-      <c r="R14" s="4">
-        <v>2</v>
-      </c>
-      <c r="S14" s="4">
-        <v>2</v>
-      </c>
-      <c r="T14">
+        <v>2</v>
+      </c>
+      <c r="R14">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="U14">
+      <c r="S14">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="V14">
+      <c r="T14">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="W14">
+      <c r="U14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X14" s="12">
+      <c r="V14" s="12">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="Y14" s="8" t="s">
+      <c r="W14" s="12"/>
+      <c r="X14" s="12">
+        <v>25</v>
+      </c>
+      <c r="Y14" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="Z14" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA14" s="17" t="s">
+      <c r="Z14" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="AB14" s="20" t="s">
+      <c r="AA14" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="AC14" s="17" t="s">
+      <c r="AB14" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD14">
+      <c r="AC14" s="37" t="str">
+        <f>+Z14</f>
+        <v>Undo a Task</v>
+      </c>
+      <c r="AD14" s="37"/>
+      <c r="AE14">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" ht="50.6" x14ac:dyDescent="0.4">
-      <c r="A15" s="8" t="s">
+      <c r="AF14">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" ht="50.6" x14ac:dyDescent="0.4">
+      <c r="A15" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="17" t="s">
+      <c r="B15" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="C15" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="E15" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G15" s="12">
+      <c r="E15" s="12">
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="H15" s="4">
-        <v>1</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
+      <c r="F15" s="4">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4">
+        <v>2</v>
+      </c>
+      <c r="J15" s="4">
+        <v>2</v>
       </c>
       <c r="K15" s="4">
         <v>2</v>
       </c>
       <c r="L15" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M15" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O15" s="4">
         <v>1</v>
       </c>
       <c r="P15" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="4">
-        <v>1</v>
-      </c>
-      <c r="R15" s="4">
-        <v>2</v>
-      </c>
-      <c r="S15" s="4">
-        <v>2</v>
-      </c>
-      <c r="T15">
+        <v>2</v>
+      </c>
+      <c r="R15">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="U15">
+      <c r="S15">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="V15">
+      <c r="T15">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="W15">
+      <c r="U15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X15" s="12">
+      <c r="V15" s="12">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="Y15" s="8" t="s">
+      <c r="W15" s="12"/>
+      <c r="X15" s="12">
+        <v>25</v>
+      </c>
+      <c r="Y15" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="Z15" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA15" s="17" t="s">
+      <c r="Z15" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="AB15" s="20" t="s">
+      <c r="AA15" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="AC15" s="17" t="s">
+      <c r="AB15" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD15">
+      <c r="AC15" s="37" t="str">
+        <f>+Z15</f>
+        <v>Redo a Task</v>
+      </c>
+      <c r="AD15" s="37"/>
+      <c r="AE15">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" ht="50.6" x14ac:dyDescent="0.4">
-      <c r="A16" s="8" t="s">
+      <c r="AF15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" ht="50.6" x14ac:dyDescent="0.4">
+      <c r="A16" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="17" t="s">
+      <c r="B16" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="C16" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="E16" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G16" s="12">
+      <c r="E16" s="12">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="H16" s="4">
-        <v>1</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
+      <c r="J16" s="4">
+        <v>2</v>
       </c>
       <c r="K16" s="4">
         <v>1</v>
       </c>
       <c r="L16" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M16" s="4">
         <v>1</v>
       </c>
       <c r="N16" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O16" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P16" s="4">
         <v>2</v>
       </c>
       <c r="Q16" s="4">
-        <v>3</v>
-      </c>
-      <c r="R16" s="4">
-        <v>2</v>
-      </c>
-      <c r="S16" s="4">
-        <v>2</v>
-      </c>
-      <c r="T16">
+        <v>2</v>
+      </c>
+      <c r="R16">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
+      <c r="S16">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
       <c r="U16">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="V16">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="W16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X16" s="12">
+      <c r="V16" s="12">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="Y16" s="8" t="s">
+      <c r="W16" s="12"/>
+      <c r="X16" s="12">
+        <v>25</v>
+      </c>
+      <c r="Y16" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="Z16" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA16" s="17" t="s">
+      <c r="Z16" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="AB16" s="20" t="s">
+      <c r="AA16" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="AC16" s="17" t="s">
+      <c r="AB16" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="AD16">
+      <c r="AC16" t="s">
+        <v>269</v>
+      </c>
+      <c r="AD16" s="37"/>
+      <c r="AE16">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:30" ht="25.75" x14ac:dyDescent="0.4">
-      <c r="A17" s="8" t="s">
+      <c r="AF16">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A17" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="17" t="s">
+      <c r="B17" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="C17" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="E17" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="12">
+      <c r="E17" s="12">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="H17" s="4">
-        <v>1</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
+      <c r="F17" s="4">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1</v>
+      </c>
+      <c r="J17" s="4">
+        <v>2</v>
       </c>
       <c r="K17" s="4">
         <v>1</v>
       </c>
       <c r="L17" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M17" s="4">
         <v>1</v>
       </c>
       <c r="N17" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O17" s="4">
         <v>1</v>
       </c>
       <c r="P17" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4">
-        <v>1</v>
-      </c>
-      <c r="R17" s="4">
-        <v>1</v>
-      </c>
-      <c r="S17" s="4">
-        <v>2</v>
-      </c>
-      <c r="T17">
+        <v>2</v>
+      </c>
+      <c r="R17">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
+      <c r="S17">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="U17">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="V17">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="W17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X17" s="12">
+      <c r="V17" s="12">
         <f t="shared" si="5"/>
         <v>16</v>
       </c>
-      <c r="Y17" s="8" t="s">
+      <c r="W17" s="12"/>
+      <c r="X17" s="12">
+        <v>15</v>
+      </c>
+      <c r="Y17" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="Z17" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA17" s="17" t="s">
+      <c r="Z17" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="AB17" s="20" t="s">
+      <c r="AA17" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="AC17" s="17" t="s">
+      <c r="AB17" s="17" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="18" spans="1:30" ht="38.15" x14ac:dyDescent="0.4">
-      <c r="A18" s="8" t="s">
+      <c r="AC17" s="40"/>
+      <c r="AD17" s="37"/>
+    </row>
+    <row r="18" spans="1:32" ht="38.15" x14ac:dyDescent="0.4">
+      <c r="A18" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="17" t="s">
+      <c r="B18" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="C18" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="E18" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G18" s="12">
+      <c r="E18" s="12">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="H18" s="4">
-        <v>1</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
+      <c r="F18" s="4">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
+      <c r="J18" s="4">
+        <v>2</v>
       </c>
       <c r="K18" s="4">
         <v>1</v>
       </c>
       <c r="L18" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M18" s="4">
         <v>1</v>
       </c>
       <c r="N18" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O18" s="4">
         <v>1</v>
       </c>
       <c r="P18" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4">
-        <v>1</v>
-      </c>
-      <c r="R18" s="4">
-        <v>1</v>
-      </c>
-      <c r="S18" s="4">
-        <v>2</v>
-      </c>
-      <c r="T18">
+        <v>2</v>
+      </c>
+      <c r="R18">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
+      <c r="S18">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="U18">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="V18">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="W18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X18" s="12">
+      <c r="V18" s="12">
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="Y18" s="8" t="s">
+      <c r="W18" s="12"/>
+      <c r="X18" s="12">
+        <v>23</v>
+      </c>
+      <c r="Y18" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="Z18" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA18" s="17" t="s">
+      <c r="Z18" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="AB18" s="20" t="s">
+      <c r="AA18" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="AC18" s="17" t="s">
+      <c r="AB18" s="17" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="19" spans="1:30" ht="63" x14ac:dyDescent="0.4">
-      <c r="A19" s="8" t="s">
+      <c r="AC18" s="40"/>
+      <c r="AD18" s="37"/>
+    </row>
+    <row r="19" spans="1:32" ht="63" x14ac:dyDescent="0.4">
+      <c r="A19" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="24" t="s">
+      <c r="B19" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="C19" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="E19" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="F19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="12">
+      <c r="E19" s="12">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="H19" s="4">
-        <v>2</v>
-      </c>
-      <c r="I19">
-        <v>3</v>
-      </c>
-      <c r="J19">
-        <v>2</v>
+      <c r="F19" s="4">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="I19" s="4">
+        <v>2</v>
+      </c>
+      <c r="J19" s="4">
+        <v>3</v>
       </c>
       <c r="K19" s="4">
         <v>2</v>
       </c>
       <c r="L19" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M19" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O19" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P19" s="4">
         <v>3</v>
       </c>
       <c r="Q19" s="4">
-        <v>2</v>
-      </c>
-      <c r="R19" s="4">
-        <v>3</v>
-      </c>
-      <c r="S19" s="4">
-        <v>3</v>
-      </c>
-      <c r="T19">
+        <v>3</v>
+      </c>
+      <c r="R19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U19">
+      <c r="S19">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="V19">
+      <c r="T19">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="W19">
+      <c r="U19">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="X19" s="12">
+      <c r="V19" s="12">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="Y19" s="8" t="s">
+      <c r="W19" s="12"/>
+      <c r="X19" s="12">
+        <v>63</v>
+      </c>
+      <c r="Y19" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="Z19" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA19" s="24" t="s">
+      <c r="Z19" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="AB19" s="20" t="s">
+      <c r="AA19" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="AC19" s="25" t="s">
+      <c r="AB19" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="AD19">
+      <c r="AC19" s="38" t="str">
+        <f>+Z19</f>
+        <v>Paste Special</v>
+      </c>
+      <c r="AD19" s="38"/>
+      <c r="AE19">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:30" ht="75.45" x14ac:dyDescent="0.4">
-      <c r="A20" s="8" t="s">
+      <c r="AF19">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" ht="75.45" x14ac:dyDescent="0.4">
+      <c r="A20" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="24" t="s">
+      <c r="B20" s="24" t="s">
         <v>206</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="C20" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="E20" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G20" s="12">
+      <c r="E20" s="12">
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="H20" s="4">
-        <v>2</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20">
+      <c r="F20" s="4">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>3</v>
+      </c>
+      <c r="I20" s="4">
+        <v>3</v>
+      </c>
+      <c r="J20" s="4">
         <v>3</v>
       </c>
       <c r="K20" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L20" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M20" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N20" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O20" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P20" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q20" s="4">
-        <v>2</v>
-      </c>
-      <c r="R20" s="4">
-        <v>4</v>
-      </c>
-      <c r="S20" s="4">
+        <v>3</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="T20">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="U20">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="V20">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="W20">
+      <c r="U20">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="X20" s="12">
+      <c r="V20" s="12">
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="Y20" s="8" t="s">
+      <c r="W20" s="12"/>
+      <c r="X20" s="12">
+        <v>23</v>
+      </c>
+      <c r="Y20" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="Z20" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA20" s="24" t="s">
+      <c r="Z20" s="24" t="s">
         <v>206</v>
       </c>
-      <c r="AB20" s="20" t="s">
+      <c r="AA20" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="AC20" s="25" t="s">
+      <c r="AB20" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="AD20">
+      <c r="AC20" s="38" t="str">
+        <f>+Z20</f>
+        <v>Go To</v>
+      </c>
+      <c r="AD20" s="38"/>
+      <c r="AE20">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" spans="1:30" ht="75.45" x14ac:dyDescent="0.4">
-      <c r="A21" s="8" t="s">
+      <c r="AF20">
         <v>23</v>
       </c>
-      <c r="B21" s="21" t="s">
+    </row>
+    <row r="21" spans="1:32" ht="75.45" x14ac:dyDescent="0.4">
+      <c r="A21" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="B21" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="C21" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="E21" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G21" s="12">
+      <c r="E21" s="12">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="H21" s="4">
-        <v>2</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
+      <c r="F21" s="4">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" s="4">
+        <v>3</v>
+      </c>
+      <c r="J21" s="4">
+        <v>2</v>
       </c>
       <c r="K21" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L21" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N21" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O21" s="4">
         <v>1</v>
       </c>
       <c r="P21" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q21" s="4">
-        <v>1</v>
-      </c>
-      <c r="R21" s="4">
-        <v>4</v>
-      </c>
-      <c r="S21" s="4">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="T21">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="U21">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="V21">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="W21">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="X21" s="12">
+      <c r="V21" s="12">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="Y21" s="8" t="s">
+      <c r="W21" s="12"/>
+      <c r="X21" s="12">
+        <v>19</v>
+      </c>
+      <c r="Y21" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="Z21" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA21" s="17" t="s">
+      <c r="Z21" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="AB21" s="20" t="s">
+      <c r="AA21" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="AC21" s="17" t="s">
+      <c r="AB21" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD21">
+      <c r="AC21" s="37" t="str">
+        <f>+Z21</f>
+        <v>Find</v>
+      </c>
+      <c r="AD21" s="37"/>
+      <c r="AE21">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="1:30" ht="50.6" x14ac:dyDescent="0.4">
-      <c r="A22" s="8" t="s">
+      <c r="AF21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" ht="50.6" x14ac:dyDescent="0.4">
+      <c r="A22" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="17" t="s">
+      <c r="B22" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="C22" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="E22" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G22" s="12">
+      <c r="E22" s="12">
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="H22" s="4">
-        <v>3</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
+      <c r="F22" s="4">
+        <v>3</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" s="4">
+        <v>4</v>
+      </c>
+      <c r="J22" s="4">
+        <v>3</v>
       </c>
       <c r="K22" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L22" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M22" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N22" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O22" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P22" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="4">
-        <v>2</v>
-      </c>
-      <c r="R22" s="4">
-        <v>3</v>
-      </c>
-      <c r="S22" s="4">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="T22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="U22">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="V22">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="W22">
+      <c r="U22">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="X22" s="12">
+      <c r="V22" s="12">
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
-      <c r="Y22" s="8" t="s">
+      <c r="W22" s="12"/>
+      <c r="X22" s="12">
+        <v>16</v>
+      </c>
+      <c r="Y22" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="Z22" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA22" s="17" t="s">
+      <c r="Z22" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="AB22" s="20" t="s">
+      <c r="AA22" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="AC22" s="17" t="s">
+      <c r="AB22" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD22">
+      <c r="AC22" s="37" t="str">
+        <f>+Z22</f>
+        <v>Replace</v>
+      </c>
+      <c r="AD22" s="37"/>
+      <c r="AE22">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="1:30" ht="50.6" x14ac:dyDescent="0.4">
-      <c r="A23" s="8" t="s">
+      <c r="AF22">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" ht="50.6" x14ac:dyDescent="0.4">
+      <c r="A23" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="17" t="s">
+      <c r="B23" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="C23" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="E23" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G23" s="12">
+      <c r="E23" s="12">
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="H23" s="4">
-        <v>1</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <v>1</v>
+      <c r="F23" s="4">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" s="4">
+        <v>3</v>
+      </c>
+      <c r="J23" s="4">
+        <v>3</v>
       </c>
       <c r="K23" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L23" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M23" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N23" s="4">
         <v>2</v>
       </c>
       <c r="O23" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P23" s="4">
         <v>2</v>
       </c>
       <c r="Q23" s="4">
-        <v>2</v>
-      </c>
-      <c r="R23" s="4">
-        <v>2</v>
-      </c>
-      <c r="S23" s="4">
-        <v>3</v>
-      </c>
-      <c r="T23">
+        <v>3</v>
+      </c>
+      <c r="R23">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="U23">
+      <c r="S23">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="V23">
+      <c r="T23">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="W23">
+      <c r="U23">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X23" s="12">
+      <c r="V23" s="12">
         <f t="shared" si="5"/>
         <v>22</v>
       </c>
-      <c r="Y23" s="8" t="s">
+      <c r="W23" s="12"/>
+      <c r="X23" s="12">
+        <v>16</v>
+      </c>
+      <c r="Y23" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="Z23" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA23" s="17" t="s">
+      <c r="Z23" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="AB23" s="20" t="s">
+      <c r="AA23" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="AC23" s="17" t="s">
+      <c r="AB23" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD23">
+      <c r="AC23" s="37" t="str">
+        <f>+Z23</f>
+        <v>Select All</v>
+      </c>
+      <c r="AD23" s="37"/>
+      <c r="AE23">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:30" ht="38.15" x14ac:dyDescent="0.4">
-      <c r="A24" s="8" t="s">
+      <c r="AF23">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" ht="38.15" x14ac:dyDescent="0.4">
+      <c r="A24" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="24" t="s">
+      <c r="B24" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="C24" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="E24" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G24" s="12">
+      <c r="E24" s="12">
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="H24" s="4">
-        <v>1</v>
-      </c>
-      <c r="I24">
-        <v>3</v>
-      </c>
-      <c r="J24">
+      <c r="F24" s="4">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24" s="4">
+        <v>3</v>
+      </c>
+      <c r="J24" s="4">
         <v>3</v>
       </c>
       <c r="K24" s="4">
@@ -6455,96 +6552,99 @@
         <v>3</v>
       </c>
       <c r="O24" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P24" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="4">
-        <v>2</v>
-      </c>
-      <c r="R24" s="4">
-        <v>2</v>
-      </c>
-      <c r="S24" s="4">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="T24">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="U24">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="V24">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="W24">
+      <c r="U24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X24" s="12">
+      <c r="V24" s="12">
         <f t="shared" si="5"/>
         <v>23</v>
       </c>
-      <c r="Y24" s="8" t="s">
+      <c r="W24" s="12"/>
+      <c r="X24" s="12">
+        <v>12</v>
+      </c>
+      <c r="Y24" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="Z24" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA24" s="24" t="s">
+      <c r="Z24" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="AB24" s="20" t="s">
+      <c r="AA24" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="AC24" s="25" t="s">
+      <c r="AB24" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="AD24">
+      <c r="AC24" s="38" t="str">
+        <f>+Z24</f>
+        <v>Default</v>
+      </c>
+      <c r="AD24" s="38"/>
+      <c r="AE24">
         <v>19</v>
       </c>
-    </row>
-    <row r="25" spans="1:30" ht="63" x14ac:dyDescent="0.4">
-      <c r="A25" s="8" t="s">
+      <c r="AF24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" ht="63" x14ac:dyDescent="0.4">
+      <c r="A25" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="17" t="s">
+      <c r="B25" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="C25" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="E25" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G25" s="12">
+      <c r="E25" s="12">
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="H25" s="4">
-        <v>2</v>
-      </c>
-      <c r="I25">
-        <v>2</v>
-      </c>
-      <c r="J25">
-        <v>2</v>
+      <c r="F25" s="4">
+        <v>2</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+      <c r="I25" s="4">
+        <v>3</v>
+      </c>
+      <c r="J25" s="4">
+        <v>3</v>
       </c>
       <c r="K25" s="4">
         <v>3</v>
       </c>
       <c r="L25" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M25" s="4">
         <v>3</v>
@@ -6553,188 +6653,194 @@
         <v>2</v>
       </c>
       <c r="O25" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P25" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4">
-        <v>2</v>
-      </c>
-      <c r="R25" s="4">
-        <v>1</v>
-      </c>
-      <c r="S25" s="4">
-        <v>3</v>
-      </c>
-      <c r="T25">
+        <v>3</v>
+      </c>
+      <c r="R25">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U25">
+      <c r="S25">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="V25">
+      <c r="T25">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="W25">
+      <c r="U25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X25" s="12">
+      <c r="V25" s="12">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="Y25" s="8" t="s">
+      <c r="W25" s="12"/>
+      <c r="X25" s="12">
+        <v>13</v>
+      </c>
+      <c r="Y25" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="Z25" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA25" s="17" t="s">
+      <c r="Z25" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="AB25" s="20" t="s">
+      <c r="AA25" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="AC25" s="17" t="s">
+      <c r="AB25" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD25">
+      <c r="AC25" s="37" t="str">
+        <f>+Z25</f>
+        <v>Print Layout</v>
+      </c>
+      <c r="AD25" s="37"/>
+      <c r="AE25">
         <v>20</v>
       </c>
-    </row>
-    <row r="26" spans="1:30" ht="63" x14ac:dyDescent="0.4">
-      <c r="A26" s="8" t="s">
+      <c r="AF25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" ht="63" x14ac:dyDescent="0.4">
+      <c r="A26" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="24" t="s">
+      <c r="B26" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="C26" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="E26" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G26" s="12">
+      <c r="E26" s="12">
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="H26" s="4">
-        <v>2</v>
-      </c>
-      <c r="I26">
-        <v>4</v>
-      </c>
-      <c r="J26">
-        <v>3</v>
+      <c r="F26" s="4">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26" s="4">
+        <v>4</v>
+      </c>
+      <c r="J26" s="4">
+        <v>4</v>
       </c>
       <c r="K26" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L26" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M26" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N26" s="4">
         <v>3</v>
       </c>
       <c r="O26" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P26" s="4">
         <v>3</v>
       </c>
       <c r="Q26" s="4">
-        <v>3</v>
-      </c>
-      <c r="R26" s="4">
-        <v>3</v>
-      </c>
-      <c r="S26" s="4">
-        <v>4</v>
-      </c>
-      <c r="T26">
+        <v>4</v>
+      </c>
+      <c r="R26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U26">
+      <c r="S26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V26">
+      <c r="T26">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="W26">
+      <c r="U26">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="X26" s="12">
+      <c r="V26" s="12">
         <f t="shared" si="5"/>
         <v>25</v>
       </c>
-      <c r="Y26" s="8" t="s">
+      <c r="W26" s="12"/>
+      <c r="X26" s="12">
+        <v>13</v>
+      </c>
+      <c r="Y26" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="Z26" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA26" s="24" t="s">
+      <c r="Z26" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="AB26" s="20" t="s">
+      <c r="AA26" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="AC26" s="17" t="s">
+      <c r="AB26" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD26">
+      <c r="AC26" s="37" t="str">
+        <f>+Z26</f>
+        <v>Web layout</v>
+      </c>
+      <c r="AD26" s="37"/>
+      <c r="AE26">
         <v>21</v>
       </c>
-    </row>
-    <row r="27" spans="1:30" ht="25.75" x14ac:dyDescent="0.4">
-      <c r="A27" s="8" t="s">
+      <c r="AF26">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A27" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="24" t="s">
+      <c r="B27" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="C27" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G27" s="12">
+      <c r="E27" s="12">
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
-      <c r="H27" s="4">
-        <v>1</v>
-      </c>
-      <c r="I27">
-        <v>3</v>
-      </c>
-      <c r="J27">
-        <v>1</v>
+      <c r="F27" s="4">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>3</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" s="4">
+        <v>3</v>
+      </c>
+      <c r="J27" s="4">
+        <v>4</v>
       </c>
       <c r="K27" s="4">
         <v>3</v>
@@ -6743,399 +6849,404 @@
         <v>4</v>
       </c>
       <c r="M27" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N27" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O27" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P27" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="4">
         <v>4</v>
       </c>
-      <c r="R27" s="4">
-        <v>1</v>
-      </c>
-      <c r="S27" s="4">
-        <v>4</v>
-      </c>
-      <c r="T27">
+      <c r="R27">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="U27">
+      <c r="S27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V27">
+      <c r="T27">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="W27">
+      <c r="U27">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="X27" s="12">
+      <c r="V27" s="12">
         <f t="shared" si="5"/>
         <v>26</v>
       </c>
-      <c r="Y27" s="8" t="s">
+      <c r="W27" s="12"/>
+      <c r="X27" s="12">
+        <v>25</v>
+      </c>
+      <c r="Y27" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="Z27" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA27" s="24" t="s">
+      <c r="Z27" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="AB27" s="20" t="s">
+      <c r="AA27" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="AC27" s="25" t="s">
+      <c r="AB27" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="AD27">
+      <c r="AC27" s="38" t="str">
+        <f>+Z27</f>
+        <v>Zoom</v>
+      </c>
+      <c r="AD27" s="38"/>
+      <c r="AE27">
         <v>22</v>
       </c>
-    </row>
-    <row r="28" spans="1:30" ht="63" x14ac:dyDescent="0.4">
-      <c r="A28" s="8" t="s">
+      <c r="AF27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32" ht="63" x14ac:dyDescent="0.4">
+      <c r="A28" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="17" t="s">
+      <c r="B28" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="C28" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="E28" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G28" s="12">
+      <c r="E28" s="12">
         <f t="shared" si="4"/>
         <v>27</v>
       </c>
-      <c r="H28" s="4">
-        <v>1</v>
-      </c>
-      <c r="I28">
-        <v>2</v>
-      </c>
-      <c r="J28">
-        <v>1</v>
+      <c r="F28" s="4">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28" s="4">
+        <v>2</v>
+      </c>
+      <c r="J28" s="4">
+        <v>2</v>
       </c>
       <c r="K28" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L28" s="4">
         <v>2</v>
       </c>
       <c r="M28" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N28" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O28" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P28" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="4">
-        <v>3</v>
-      </c>
-      <c r="R28" s="4">
-        <v>1</v>
-      </c>
-      <c r="S28" s="4">
-        <v>4</v>
-      </c>
-      <c r="T28">
+        <v>4</v>
+      </c>
+      <c r="R28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="U28">
+      <c r="S28">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="V28">
+      <c r="T28">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="W28">
+      <c r="U28">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="X28" s="12">
+      <c r="V28" s="12">
         <f t="shared" si="5"/>
         <v>27</v>
       </c>
-      <c r="Y28" s="8" t="s">
+      <c r="W28" s="12"/>
+      <c r="X28" s="12">
+        <v>9</v>
+      </c>
+      <c r="Y28" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="Z28" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA28" s="17" t="s">
+      <c r="Z28" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="AB28" s="20" t="s">
+      <c r="AA28" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="AC28" s="17" t="s">
+      <c r="AB28" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="AD28">
+      <c r="AC28" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="AD28" s="37"/>
+      <c r="AE28">
         <v>23</v>
       </c>
-    </row>
-    <row r="29" spans="1:30" ht="50.6" x14ac:dyDescent="0.4">
-      <c r="A29" s="8" t="s">
+      <c r="AF28">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32" ht="50.6" x14ac:dyDescent="0.4">
+      <c r="A29" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="17" t="s">
+      <c r="B29" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="C29" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="E29" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G29" s="12">
+      <c r="E29" s="12">
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
-      <c r="H29" s="4">
-        <v>1</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-      <c r="J29">
-        <v>2</v>
+      <c r="F29" s="4">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29" s="4">
+        <v>2</v>
+      </c>
+      <c r="J29" s="4">
+        <v>3</v>
       </c>
       <c r="K29" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L29" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M29" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N29" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O29" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P29" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q29" s="4">
-        <v>1</v>
-      </c>
-      <c r="R29" s="4">
-        <v>2</v>
-      </c>
-      <c r="S29" s="4">
-        <v>2</v>
-      </c>
-      <c r="T29">
+        <v>2</v>
+      </c>
+      <c r="R29">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="U29">
+      <c r="S29">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="V29">
+      <c r="T29">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="W29">
+      <c r="U29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X29" s="12">
+      <c r="V29" s="12">
         <f t="shared" si="5"/>
         <v>28</v>
       </c>
-      <c r="Y29" s="8" t="s">
+      <c r="W29" s="12"/>
+      <c r="X29" s="12">
+        <v>9</v>
+      </c>
+      <c r="Y29" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="Z29" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA29" s="17" t="s">
+      <c r="Z29" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="AB29" s="20" t="s">
+      <c r="AA29" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="AC29" s="17" t="s">
+      <c r="AB29" s="17" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="30" spans="1:30" ht="63" x14ac:dyDescent="0.4">
-      <c r="A30" s="8" t="s">
+      <c r="AC29" s="40"/>
+      <c r="AD29" s="37"/>
+    </row>
+    <row r="30" spans="1:32" ht="63" x14ac:dyDescent="0.4">
+      <c r="A30" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="17" t="s">
+      <c r="B30" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="C30" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="E30" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G30" s="12">
+      <c r="E30" s="12">
         <f t="shared" si="4"/>
         <v>29</v>
       </c>
-      <c r="H30" s="4">
-        <v>3</v>
-      </c>
-      <c r="I30">
-        <v>3</v>
-      </c>
-      <c r="J30">
-        <v>2</v>
+      <c r="F30" s="4">
+        <v>3</v>
+      </c>
+      <c r="G30">
+        <v>3</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+      <c r="I30" s="4">
+        <v>3</v>
+      </c>
+      <c r="J30" s="4">
+        <v>4</v>
       </c>
       <c r="K30" s="4">
         <v>3</v>
       </c>
       <c r="L30" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M30" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N30" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O30" s="4">
         <v>2</v>
       </c>
       <c r="P30" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q30" s="4">
-        <v>2</v>
-      </c>
-      <c r="R30" s="4">
-        <v>3</v>
-      </c>
-      <c r="S30" s="4">
-        <v>4</v>
-      </c>
-      <c r="T30">
+        <v>4</v>
+      </c>
+      <c r="R30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U30">
+      <c r="S30">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="V30">
+      <c r="T30">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="W30">
+      <c r="U30">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="X30" s="12">
+      <c r="V30" s="12">
         <f t="shared" si="5"/>
         <v>29</v>
       </c>
-      <c r="Y30" s="8" t="s">
+      <c r="W30" s="12"/>
+      <c r="X30" s="12">
+        <v>9</v>
+      </c>
+      <c r="Y30" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="Z30" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA30" s="17" t="s">
+      <c r="Z30" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="AB30" s="20" t="s">
+      <c r="AA30" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="AC30" s="17" t="s">
+      <c r="AB30" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD30">
+      <c r="AC30" s="37" t="str">
+        <f>+Z30</f>
+        <v>Date/Time</v>
+      </c>
+      <c r="AD30" s="37"/>
+      <c r="AE30">
         <v>24</v>
       </c>
-    </row>
-    <row r="31" spans="1:30" ht="63" x14ac:dyDescent="0.4">
-      <c r="A31" s="8" t="s">
+      <c r="AF30">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32" ht="63" x14ac:dyDescent="0.4">
+      <c r="A31" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="17" t="s">
+      <c r="B31" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="C31" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="E31" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G31" s="12">
+      <c r="E31" s="12">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="H31" s="4">
-        <v>1</v>
-      </c>
-      <c r="I31">
-        <v>2</v>
-      </c>
-      <c r="J31">
-        <v>4</v>
+      <c r="F31" s="4">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+      <c r="H31">
+        <v>4</v>
+      </c>
+      <c r="I31" s="4">
+        <v>2</v>
+      </c>
+      <c r="J31" s="4">
+        <v>2</v>
       </c>
       <c r="K31" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L31" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M31" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N31" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O31" s="4">
         <v>3</v>
@@ -7144,283 +7255,292 @@
         <v>3</v>
       </c>
       <c r="Q31" s="4">
-        <v>3</v>
-      </c>
-      <c r="R31" s="4">
-        <v>3</v>
-      </c>
-      <c r="S31" s="4">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="R31">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S31">
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="T31">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="U31">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="V31">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="W31">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="X31" s="12">
+      <c r="V31" s="12">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
-      <c r="Y31" s="8" t="s">
+      <c r="W31" s="12"/>
+      <c r="X31" s="12">
+        <v>9</v>
+      </c>
+      <c r="Y31" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="Z31" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA31" s="17" t="s">
+      <c r="Z31" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="AB31" s="20" t="s">
+      <c r="AA31" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="AC31" s="17" t="s">
+      <c r="AB31" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD31">
+      <c r="AC31" s="37" t="str">
+        <f>+Z31</f>
+        <v>Symbol</v>
+      </c>
+      <c r="AD31" s="37"/>
+      <c r="AE31">
         <v>25</v>
       </c>
-    </row>
-    <row r="32" spans="1:30" ht="50.6" x14ac:dyDescent="0.4">
-      <c r="A32" s="8" t="s">
+      <c r="AF31">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32" ht="50.6" x14ac:dyDescent="0.4">
+      <c r="A32" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="24" t="s">
+      <c r="B32" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="C32" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G32" s="12">
+      <c r="E32" s="12">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="H32" s="4">
-        <v>3</v>
-      </c>
-      <c r="I32">
-        <v>1</v>
-      </c>
-      <c r="J32">
-        <v>3</v>
+      <c r="F32" s="4">
+        <v>3</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>3</v>
+      </c>
+      <c r="I32" s="4">
+        <v>3</v>
+      </c>
+      <c r="J32" s="4">
+        <v>4</v>
       </c>
       <c r="K32" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L32" s="4">
         <v>4</v>
       </c>
       <c r="M32" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N32" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O32" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P32" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="4">
-        <v>1</v>
-      </c>
-      <c r="R32" s="4">
-        <v>1</v>
-      </c>
-      <c r="S32" s="4">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="R32">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S32">
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="T32">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="U32">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="V32">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="W32">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="X32" s="12">
+      <c r="V32" s="12">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
-      <c r="Y32" s="8" t="s">
+      <c r="W32" s="12"/>
+      <c r="X32" s="12">
+        <v>6</v>
+      </c>
+      <c r="Y32" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="Z32" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA32" s="24" t="s">
+      <c r="Z32" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="AB32" s="20" t="s">
+      <c r="AA32" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="AC32" s="17" t="s">
+      <c r="AB32" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD32">
+      <c r="AC32" s="37" t="str">
+        <f>+Z32</f>
+        <v>Bookmark</v>
+      </c>
+      <c r="AD32" s="37"/>
+      <c r="AE32">
         <v>26</v>
       </c>
-    </row>
-    <row r="33" spans="1:30" ht="38.15" x14ac:dyDescent="0.4">
-      <c r="A33" s="8" t="s">
+      <c r="AF32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:32" ht="38.15" x14ac:dyDescent="0.4">
+      <c r="A33" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="17" t="s">
+      <c r="B33" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="E33" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G33" s="12">
+      <c r="E33" s="12">
         <f t="shared" si="4"/>
         <v>32</v>
       </c>
-      <c r="H33" s="4">
-        <v>1</v>
-      </c>
-      <c r="I33">
-        <v>3</v>
-      </c>
-      <c r="J33">
-        <v>1</v>
+      <c r="F33" s="4">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>3</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33" s="4">
+        <v>2</v>
+      </c>
+      <c r="J33" s="4">
+        <v>3</v>
       </c>
       <c r="K33" s="4">
         <v>2</v>
       </c>
       <c r="L33" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M33" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N33" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O33" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P33" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="4">
-        <v>2</v>
-      </c>
-      <c r="R33" s="4">
-        <v>1</v>
-      </c>
-      <c r="S33" s="4">
+        <v>4</v>
+      </c>
+      <c r="R33">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S33">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="T33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="U33">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="V33">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="W33">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="X33" s="12">
+      <c r="V33" s="12">
         <f t="shared" si="5"/>
         <v>32</v>
       </c>
-      <c r="Y33" s="8" t="s">
+      <c r="W33" s="12"/>
+      <c r="X33" s="12">
+        <v>5</v>
+      </c>
+      <c r="Y33" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="Z33" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA33" s="17" t="s">
+      <c r="Z33" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="AB33" s="20" t="s">
+      <c r="AA33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="AC33" s="17" t="s">
+      <c r="AB33" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD33">
+      <c r="AC33" s="37" t="str">
+        <f>+Z33</f>
+        <v>Hyperlink</v>
+      </c>
+      <c r="AD33" s="37"/>
+      <c r="AE33">
         <v>27</v>
       </c>
-    </row>
-    <row r="34" spans="1:30" ht="63" x14ac:dyDescent="0.4">
-      <c r="A34" s="8" t="s">
+      <c r="AF33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32" ht="63" x14ac:dyDescent="0.4">
+      <c r="A34" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" s="17" t="s">
+      <c r="B34" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="C34" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="E34" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G34" s="12">
+      <c r="E34" s="12">
         <f t="shared" si="4"/>
         <v>33</v>
       </c>
-      <c r="H34" s="4">
-        <v>1</v>
-      </c>
-      <c r="I34">
-        <v>1</v>
-      </c>
-      <c r="J34">
-        <v>1</v>
+      <c r="F34" s="4">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34" s="4">
+        <v>2</v>
+      </c>
+      <c r="J34" s="4">
+        <v>2</v>
       </c>
       <c r="K34" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L34" s="4">
         <v>2</v>
@@ -7432,194 +7552,200 @@
         <v>2</v>
       </c>
       <c r="O34" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P34" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="4">
-        <v>1</v>
-      </c>
-      <c r="R34" s="4">
-        <v>1</v>
-      </c>
-      <c r="S34" s="4">
-        <v>4</v>
-      </c>
-      <c r="T34">
+        <v>4</v>
+      </c>
+      <c r="R34">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
+      <c r="S34">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="T34">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
       <c r="U34">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="V34">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="W34">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="X34" s="12">
+      <c r="V34" s="12">
         <f t="shared" si="5"/>
         <v>33</v>
       </c>
-      <c r="Y34" s="8" t="s">
+      <c r="W34" s="12"/>
+      <c r="X34" s="12">
+        <v>13</v>
+      </c>
+      <c r="Y34" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="Z34" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA34" s="17" t="s">
+      <c r="Z34" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="AB34" s="20" t="s">
+      <c r="AA34" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="AC34" s="17" t="s">
+      <c r="AB34" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD34">
+      <c r="AC34" s="37" t="str">
+        <f>+Z34</f>
+        <v>Font</v>
+      </c>
+      <c r="AD34" s="37"/>
+      <c r="AE34">
         <v>28</v>
       </c>
-    </row>
-    <row r="35" spans="1:30" ht="63" x14ac:dyDescent="0.4">
-      <c r="A35" s="8" t="s">
+      <c r="AF34">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:32" ht="63" x14ac:dyDescent="0.4">
+      <c r="A35" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="17" t="s">
+      <c r="B35" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="C35" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="E35" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G35" s="12">
+      <c r="E35" s="12">
         <f t="shared" si="4"/>
         <v>34</v>
       </c>
-      <c r="H35" s="4">
-        <v>3</v>
-      </c>
-      <c r="I35">
-        <v>2</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
+      <c r="F35" s="4">
+        <v>3</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35" s="4">
+        <v>2</v>
+      </c>
+      <c r="J35" s="4">
+        <v>2</v>
       </c>
       <c r="K35" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L35" s="4">
         <v>2</v>
       </c>
       <c r="M35" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N35" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O35" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P35" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="4">
         <v>3</v>
       </c>
-      <c r="R35" s="4">
-        <v>1</v>
-      </c>
-      <c r="S35" s="4">
-        <v>3</v>
-      </c>
-      <c r="T35">
+      <c r="R35">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="U35">
+      <c r="S35">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="V35">
+      <c r="T35">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="W35">
+      <c r="U35">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X35" s="12">
+      <c r="V35" s="12">
         <f t="shared" si="5"/>
         <v>34</v>
       </c>
-      <c r="Y35" s="8" t="s">
+      <c r="W35" s="12"/>
+      <c r="X35" s="12">
+        <v>23</v>
+      </c>
+      <c r="Y35" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="Z35" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA35" s="17" t="s">
+      <c r="Z35" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="AB35" s="20" t="s">
+      <c r="AA35" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="AC35" s="17" t="s">
+      <c r="AB35" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD35">
+      <c r="AC35" s="37" t="str">
+        <f>+Z35</f>
+        <v>Paragraph</v>
+      </c>
+      <c r="AD35" s="37"/>
+      <c r="AE35">
         <v>29</v>
       </c>
-    </row>
-    <row r="36" spans="1:30" ht="75.45" x14ac:dyDescent="0.4">
-      <c r="A36" s="8" t="s">
+      <c r="AF35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:32" ht="75.45" x14ac:dyDescent="0.4">
+      <c r="A36" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" s="17" t="s">
+      <c r="B36" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="C36" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="E36" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G36" s="12">
+      <c r="E36" s="12">
         <f t="shared" si="4"/>
         <v>35</v>
       </c>
-      <c r="H36" s="4">
-        <v>2</v>
-      </c>
-      <c r="I36">
-        <v>3</v>
-      </c>
-      <c r="J36">
+      <c r="F36" s="4">
+        <v>2</v>
+      </c>
+      <c r="G36">
+        <v>3</v>
+      </c>
+      <c r="H36">
+        <v>2</v>
+      </c>
+      <c r="I36" s="4">
+        <v>3</v>
+      </c>
+      <c r="J36" s="4">
         <v>2</v>
       </c>
       <c r="K36" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L36" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M36" s="4">
         <v>2</v>
@@ -7628,187 +7754,193 @@
         <v>4</v>
       </c>
       <c r="O36" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P36" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="4">
         <v>4</v>
       </c>
-      <c r="R36" s="4">
-        <v>1</v>
-      </c>
-      <c r="S36" s="4">
-        <v>4</v>
-      </c>
-      <c r="T36">
+      <c r="R36">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U36">
+      <c r="S36">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="V36">
+      <c r="T36">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="W36">
+      <c r="U36">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="X36" s="12">
+      <c r="V36" s="12">
         <f t="shared" si="5"/>
         <v>35</v>
       </c>
-      <c r="Y36" s="8" t="s">
+      <c r="W36" s="12"/>
+      <c r="X36" s="12">
+        <v>19</v>
+      </c>
+      <c r="Y36" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="Z36" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA36" s="17" t="s">
+      <c r="Z36" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="AB36" s="20" t="s">
+      <c r="AA36" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="AC36" s="17" t="s">
+      <c r="AB36" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD36">
+      <c r="AC36" s="37" t="str">
+        <f>+Z36</f>
+        <v>Bullets/Numbering</v>
+      </c>
+      <c r="AD36" s="37"/>
+      <c r="AE36">
         <v>30</v>
       </c>
-    </row>
-    <row r="37" spans="1:30" ht="100.3" x14ac:dyDescent="0.4">
-      <c r="A37" s="8" t="s">
+      <c r="AF36">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:32" ht="100.3" x14ac:dyDescent="0.4">
+      <c r="A37" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="17" t="s">
+      <c r="B37" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="D37" s="20" t="s">
+      <c r="C37" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="E37" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F37" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G37" s="12">
+      <c r="E37" s="12">
         <f t="shared" si="4"/>
         <v>36</v>
       </c>
-      <c r="H37" s="4">
-        <v>2</v>
-      </c>
-      <c r="I37">
-        <v>1</v>
-      </c>
-      <c r="J37">
-        <v>3</v>
+      <c r="F37" s="4">
+        <v>2</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>3</v>
+      </c>
+      <c r="I37" s="4">
+        <v>3</v>
+      </c>
+      <c r="J37" s="4">
+        <v>2</v>
       </c>
       <c r="K37" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L37" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M37" s="4">
         <v>2</v>
       </c>
       <c r="N37" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O37" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P37" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q37" s="4">
         <v>1</v>
       </c>
-      <c r="R37" s="4">
-        <v>2</v>
-      </c>
-      <c r="S37" s="4">
-        <v>1</v>
-      </c>
-      <c r="T37">
+      <c r="R37">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="U37">
+      <c r="S37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="V37">
+      <c r="T37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="W37">
+      <c r="U37">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="X37" s="12">
+      <c r="V37" s="12">
         <f t="shared" si="5"/>
         <v>36</v>
       </c>
-      <c r="Y37" s="8" t="s">
+      <c r="W37" s="12"/>
+      <c r="X37" s="12">
+        <v>19</v>
+      </c>
+      <c r="Y37" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="Z37" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA37" s="17" t="s">
+      <c r="Z37" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="AB37" s="20" t="s">
+      <c r="AA37" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="AC37" s="17" t="s">
+      <c r="AB37" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD37">
+      <c r="AC37" s="37" t="str">
+        <f>+Z37</f>
+        <v>Change Case</v>
+      </c>
+      <c r="AD37" s="37"/>
+      <c r="AE37">
         <v>31</v>
       </c>
-    </row>
-    <row r="38" spans="1:30" ht="63" x14ac:dyDescent="0.4">
-      <c r="A38" s="8" t="s">
+      <c r="AF37">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:32" ht="63" x14ac:dyDescent="0.4">
+      <c r="A38" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="17" t="s">
+      <c r="B38" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="D38" s="20" t="s">
+      <c r="C38" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="E38" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F38" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G38" s="12">
+      <c r="E38" s="12">
         <f t="shared" si="4"/>
         <v>37</v>
       </c>
-      <c r="H38" s="4">
-        <v>4</v>
-      </c>
-      <c r="I38">
-        <v>4</v>
-      </c>
-      <c r="J38">
+      <c r="F38" s="4">
+        <v>4</v>
+      </c>
+      <c r="G38">
+        <v>4</v>
+      </c>
+      <c r="H38">
+        <v>4</v>
+      </c>
+      <c r="I38" s="4">
+        <v>3</v>
+      </c>
+      <c r="J38" s="4">
         <v>4</v>
       </c>
       <c r="K38" s="4">
@@ -7818,200 +7950,206 @@
         <v>4</v>
       </c>
       <c r="M38" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N38" s="4">
         <v>4</v>
       </c>
       <c r="O38" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P38" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q38" s="4">
         <v>2</v>
       </c>
-      <c r="R38" s="4">
-        <v>2</v>
-      </c>
-      <c r="S38" s="4">
-        <v>2</v>
-      </c>
-      <c r="T38">
+      <c r="R38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="S38">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
       <c r="U38">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="V38">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="W38">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="X38" s="12">
+      <c r="V38" s="12">
         <f t="shared" si="5"/>
         <v>37</v>
       </c>
-      <c r="Y38" s="8" t="s">
+      <c r="W38" s="12"/>
+      <c r="X38" s="12">
+        <v>19</v>
+      </c>
+      <c r="Y38" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="Z38" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA38" s="17" t="s">
+      <c r="Z38" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="AB38" s="20" t="s">
+      <c r="AA38" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="AC38" s="17" t="s">
+      <c r="AB38" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD38">
+      <c r="AC38" s="37" t="str">
+        <f>+Z38</f>
+        <v>Background</v>
+      </c>
+      <c r="AD38" s="37"/>
+      <c r="AE38">
         <v>32</v>
       </c>
-    </row>
-    <row r="39" spans="1:30" ht="38.15" x14ac:dyDescent="0.4">
-      <c r="A39" s="8" t="s">
+      <c r="AF38">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:32" ht="38.15" x14ac:dyDescent="0.4">
+      <c r="A39" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B39" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="C39" s="17" t="s">
+      <c r="B39" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="C39" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="E39" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F39" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G39" s="12">
+      <c r="E39" s="12">
         <f t="shared" si="4"/>
         <v>38</v>
       </c>
-      <c r="H39" s="4">
-        <v>1</v>
-      </c>
-      <c r="I39">
-        <v>1</v>
-      </c>
-      <c r="J39">
-        <v>1</v>
+      <c r="F39" s="4">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39" s="4">
+        <v>2</v>
+      </c>
+      <c r="J39" s="4">
+        <v>4</v>
       </c>
       <c r="K39" s="4">
         <v>2</v>
       </c>
       <c r="L39" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M39" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N39" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O39" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P39" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q39" s="4">
-        <v>3</v>
-      </c>
-      <c r="R39" s="4">
-        <v>3</v>
-      </c>
-      <c r="S39" s="4">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="R39">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="S39">
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="T39">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="U39">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="V39">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="W39">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="X39" s="12">
+      <c r="V39" s="12">
         <f t="shared" si="5"/>
         <v>38</v>
       </c>
-      <c r="Y39" s="8" t="s">
+      <c r="W39" s="12"/>
+      <c r="X39" s="12">
+        <v>36</v>
+      </c>
+      <c r="Y39" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="Z39" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA39" s="17" t="s">
+      <c r="Z39" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="AB39" s="20" t="s">
+      <c r="AA39" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="AC39" s="17" t="s">
+      <c r="AB39" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD39">
+      <c r="AC39" s="37" t="str">
+        <f>+Z39</f>
+        <v>Check Spell</v>
+      </c>
+      <c r="AD39" s="37"/>
+      <c r="AE39">
         <v>33</v>
       </c>
-    </row>
-    <row r="40" spans="1:30" ht="38.15" x14ac:dyDescent="0.4">
-      <c r="A40" s="8" t="s">
+      <c r="AF39">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:32" ht="38.15" x14ac:dyDescent="0.4">
+      <c r="A40" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B40" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="17" t="s">
+      <c r="B40" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="D40" s="20" t="s">
+      <c r="C40" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="E40" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F40" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G40" s="12">
+      <c r="E40" s="12">
         <f t="shared" si="4"/>
         <v>39</v>
       </c>
-      <c r="H40" s="4">
-        <v>1</v>
-      </c>
-      <c r="I40">
-        <v>1</v>
-      </c>
-      <c r="J40">
-        <v>1</v>
+      <c r="F40" s="4">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" s="4">
+        <v>3</v>
+      </c>
+      <c r="J40" s="4">
+        <v>4</v>
       </c>
       <c r="K40" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L40" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M40" s="4">
         <v>1</v>
@@ -8020,203 +8158,209 @@
         <v>3</v>
       </c>
       <c r="O40" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P40" s="4">
         <v>3</v>
       </c>
       <c r="Q40" s="4">
-        <v>3</v>
-      </c>
-      <c r="R40" s="4">
-        <v>3</v>
-      </c>
-      <c r="S40" s="4">
-        <v>4</v>
-      </c>
-      <c r="T40">
+        <v>4</v>
+      </c>
+      <c r="R40">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="U40">
+      <c r="S40">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V40">
+      <c r="T40">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="W40">
+      <c r="U40">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="X40" s="12">
+      <c r="V40" s="12">
         <f t="shared" si="5"/>
         <v>39</v>
       </c>
-      <c r="Y40" s="8" t="s">
+      <c r="W40" s="12"/>
+      <c r="X40" s="12">
+        <v>38</v>
+      </c>
+      <c r="Y40" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="Z40" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA40" s="17" t="s">
+      <c r="Z40" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="AB40" s="20" t="s">
+      <c r="AA40" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="AC40" s="17" t="s">
+      <c r="AB40" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD40">
+      <c r="AC40" s="37" t="str">
+        <f>+Z40</f>
+        <v>Check Grammer</v>
+      </c>
+      <c r="AD40" s="37"/>
+      <c r="AE40">
         <v>34</v>
       </c>
-    </row>
-    <row r="41" spans="1:30" ht="63" x14ac:dyDescent="0.4">
-      <c r="A41" s="8" t="s">
+      <c r="AF40">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:32" ht="63" x14ac:dyDescent="0.4">
+      <c r="A41" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C41" s="24" t="s">
+      <c r="B41" s="24" t="s">
         <v>244</v>
       </c>
-      <c r="D41" s="20" t="s">
+      <c r="C41" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="E41" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F41" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G41" s="12">
+      <c r="E41" s="12">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="H41" s="4">
-        <v>4</v>
-      </c>
-      <c r="I41">
-        <v>4</v>
-      </c>
-      <c r="J41">
+      <c r="F41" s="4">
+        <v>4</v>
+      </c>
+      <c r="G41">
+        <v>4</v>
+      </c>
+      <c r="H41">
+        <v>3</v>
+      </c>
+      <c r="I41" s="4">
+        <v>4</v>
+      </c>
+      <c r="J41" s="4">
         <v>3</v>
       </c>
       <c r="K41" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L41" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M41" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N41" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O41" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P41" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q41" s="4">
-        <v>4</v>
-      </c>
-      <c r="R41" s="4">
-        <v>4</v>
-      </c>
-      <c r="S41" s="4">
+        <v>1</v>
+      </c>
+      <c r="R41">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="S41">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="T41">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="U41">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="V41">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="W41">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="X41" s="12">
+      <c r="V41" s="12">
         <f t="shared" si="5"/>
         <v>40</v>
       </c>
-      <c r="Y41" s="8" t="s">
+      <c r="W41" s="12"/>
+      <c r="X41" s="12">
+        <v>17</v>
+      </c>
+      <c r="Y41" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="Z41" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA41" s="24" t="s">
+      <c r="Z41" s="24" t="s">
         <v>244</v>
       </c>
-      <c r="AB41" s="20" t="s">
+      <c r="AA41" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="AC41" s="17" t="s">
+      <c r="AB41" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD41">
+      <c r="AC41" s="37" t="str">
+        <f>+Z41</f>
+        <v>Speech</v>
+      </c>
+      <c r="AD41" s="37"/>
+      <c r="AE41">
         <v>35</v>
       </c>
-    </row>
-    <row r="42" spans="1:30" ht="75.45" x14ac:dyDescent="0.4">
-      <c r="A42" s="8" t="s">
+      <c r="AF41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:32" ht="75.45" x14ac:dyDescent="0.4">
+      <c r="A42" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="31" t="s">
+      <c r="B42" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="C42" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="E42" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F42" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G42" s="12">
+      <c r="E42" s="12">
         <f t="shared" si="4"/>
         <v>41</v>
       </c>
-      <c r="H42" s="4">
-        <v>2</v>
-      </c>
-      <c r="I42">
-        <v>3</v>
-      </c>
-      <c r="J42">
-        <v>3</v>
+      <c r="F42" s="4">
+        <v>2</v>
+      </c>
+      <c r="G42">
+        <v>3</v>
+      </c>
+      <c r="H42">
+        <v>3</v>
+      </c>
+      <c r="I42" s="4">
+        <v>4</v>
+      </c>
+      <c r="J42" s="4">
+        <v>4</v>
       </c>
       <c r="K42" s="4">
         <v>4</v>
       </c>
       <c r="L42" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M42" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N42" s="4">
         <v>3</v>
       </c>
       <c r="O42" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P42" s="4">
         <v>3</v>
@@ -8224,97 +8368,100 @@
       <c r="Q42" s="4">
         <v>4</v>
       </c>
-      <c r="R42" s="4">
-        <v>3</v>
-      </c>
-      <c r="S42" s="4">
-        <v>4</v>
-      </c>
-      <c r="T42">
+      <c r="R42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U42">
+      <c r="S42">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V42">
+      <c r="T42">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="W42">
+      <c r="U42">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="X42" s="12">
+      <c r="V42" s="12">
         <f t="shared" si="5"/>
         <v>41</v>
       </c>
-      <c r="Y42" s="8" t="s">
+      <c r="W42" s="12"/>
+      <c r="X42" s="12">
+        <v>80</v>
+      </c>
+      <c r="Y42" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="Z42" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA42" s="31" t="s">
+      <c r="Z42" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="AB42" s="20" t="s">
+      <c r="AA42" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="AC42" s="17" t="s">
+      <c r="AB42" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD42">
+      <c r="AC42" s="37" t="str">
+        <f>+Z42</f>
+        <v>Mail Merge</v>
+      </c>
+      <c r="AD42" s="37"/>
+      <c r="AE42">
         <v>36</v>
       </c>
-    </row>
-    <row r="43" spans="1:30" ht="100.3" x14ac:dyDescent="0.4">
-      <c r="A43" s="8" t="s">
+      <c r="AF42">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:32" ht="100.3" x14ac:dyDescent="0.4">
+      <c r="A43" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="B43" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C43" s="24" t="s">
+      <c r="B43" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="20" t="s">
+      <c r="C43" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="E43" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F43" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G43" s="12">
+      <c r="E43" s="12">
         <f t="shared" si="4"/>
         <v>42</v>
       </c>
-      <c r="H43" s="4">
-        <v>3</v>
-      </c>
-      <c r="I43">
-        <v>4</v>
-      </c>
-      <c r="J43">
+      <c r="F43" s="4">
+        <v>3</v>
+      </c>
+      <c r="G43">
+        <v>4</v>
+      </c>
+      <c r="H43">
+        <v>4</v>
+      </c>
+      <c r="I43" s="4">
+        <v>4</v>
+      </c>
+      <c r="J43" s="4">
         <v>4</v>
       </c>
       <c r="K43" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L43" s="4">
         <v>4</v>
       </c>
       <c r="M43" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N43" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O43" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P43" s="4">
         <v>2</v>
@@ -8322,85 +8469,88 @@
       <c r="Q43" s="4">
         <v>4</v>
       </c>
-      <c r="R43" s="4">
-        <v>2</v>
-      </c>
-      <c r="S43" s="4">
-        <v>4</v>
-      </c>
-      <c r="T43">
+      <c r="R43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="S43">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="T43">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
       <c r="U43">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="V43">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="W43">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="X43" s="12">
+      <c r="V43" s="12">
         <f t="shared" si="5"/>
         <v>42</v>
       </c>
-      <c r="Y43" s="8" t="s">
+      <c r="W43" s="12"/>
+      <c r="X43" s="12">
+        <v>61</v>
+      </c>
+      <c r="Y43" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="Z43" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA43" s="24" t="s">
+      <c r="Z43" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="AB43" s="20" t="s">
+      <c r="AA43" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="AC43" s="17" t="s">
+      <c r="AB43" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD43">
+      <c r="AC43" s="37" t="str">
+        <f>+Z43</f>
+        <v>Macro</v>
+      </c>
+      <c r="AD43" s="37"/>
+      <c r="AE43">
         <v>37</v>
       </c>
-    </row>
-    <row r="44" spans="1:30" ht="50.6" x14ac:dyDescent="0.4">
-      <c r="A44" s="8" t="s">
+      <c r="AF43">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:32" ht="50.6" x14ac:dyDescent="0.4">
+      <c r="A44" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B44" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="C44" s="24" t="s">
+      <c r="B44" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="D44" s="20" t="s">
+      <c r="C44" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="E44" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G44" s="12">
+      <c r="E44" s="12">
         <f t="shared" si="4"/>
         <v>43</v>
       </c>
-      <c r="H44" s="4">
-        <v>2</v>
-      </c>
-      <c r="I44">
-        <v>2</v>
-      </c>
-      <c r="J44">
-        <v>3</v>
+      <c r="F44" s="4">
+        <v>2</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
+      <c r="H44">
+        <v>3</v>
+      </c>
+      <c r="I44" s="4">
+        <v>3</v>
+      </c>
+      <c r="J44" s="4">
+        <v>2</v>
       </c>
       <c r="K44" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L44" s="4">
         <v>2</v>
@@ -8409,7 +8559,7 @@
         <v>2</v>
       </c>
       <c r="N44" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O44" s="4">
         <v>2</v>
@@ -8418,96 +8568,99 @@
         <v>1</v>
       </c>
       <c r="Q44" s="4">
-        <v>2</v>
-      </c>
-      <c r="R44" s="4">
-        <v>1</v>
-      </c>
-      <c r="S44" s="4">
-        <v>1</v>
-      </c>
-      <c r="T44">
+        <v>1</v>
+      </c>
+      <c r="R44">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="U44">
+      <c r="S44">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="V44">
+      <c r="T44">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="W44">
+      <c r="U44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X44" s="12">
+      <c r="V44" s="12">
         <f t="shared" si="5"/>
         <v>43</v>
       </c>
-      <c r="Y44" s="8" t="s">
+      <c r="W44" s="12"/>
+      <c r="X44" s="12">
+        <v>13</v>
+      </c>
+      <c r="Y44" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="Z44" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA44" s="24" t="s">
+      <c r="Z44" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="AB44" s="20" t="s">
+      <c r="AA44" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="AC44" s="17" t="s">
+      <c r="AB44" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD44">
+      <c r="AC44" s="37" t="str">
+        <f>+Z44</f>
+        <v>Set Options</v>
+      </c>
+      <c r="AD44" s="37"/>
+      <c r="AE44">
         <v>38</v>
       </c>
-    </row>
-    <row r="45" spans="1:30" ht="25.75" x14ac:dyDescent="0.4">
-      <c r="A45" s="8" t="s">
+      <c r="AF44">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:32" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A45" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="B45" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C45" s="17" t="s">
+      <c r="B45" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="D45" s="20" t="s">
+      <c r="C45" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="E45" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F45" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G45" s="12">
+      <c r="E45" s="12">
         <f t="shared" si="4"/>
         <v>44</v>
       </c>
-      <c r="H45" s="4">
-        <v>1</v>
-      </c>
-      <c r="I45">
-        <v>2</v>
-      </c>
-      <c r="J45">
-        <v>1</v>
+      <c r="F45" s="4">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>2</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45" s="4">
+        <v>2</v>
+      </c>
+      <c r="J45" s="4">
+        <v>2</v>
       </c>
       <c r="K45" s="4">
         <v>2</v>
       </c>
       <c r="L45" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M45" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N45" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O45" s="4">
         <v>3</v>
@@ -8518,468 +8671,470 @@
       <c r="Q45" s="4">
         <v>3</v>
       </c>
-      <c r="R45" s="4">
-        <v>1</v>
-      </c>
-      <c r="S45" s="4">
-        <v>3</v>
+      <c r="R45">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="T45">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="U45">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="V45">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="W45">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="X45" s="12">
+      <c r="V45" s="12">
         <f t="shared" si="5"/>
         <v>44</v>
       </c>
-      <c r="Y45" s="8" t="s">
+      <c r="W45" s="12"/>
+      <c r="X45" s="12">
+        <v>19</v>
+      </c>
+      <c r="Y45" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="Z45" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA45" s="17" t="s">
+      <c r="Z45" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="AB45" s="20" t="s">
+      <c r="AA45" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="AC45" s="17" t="s">
+      <c r="AB45" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="AD45">
+      <c r="AC45" s="40" t="s">
+        <v>272</v>
+      </c>
+      <c r="AD45" s="37"/>
+      <c r="AE45">
         <v>39</v>
       </c>
-    </row>
-    <row r="46" spans="1:30" ht="38.15" x14ac:dyDescent="0.4">
-      <c r="A46" s="8" t="s">
+      <c r="AF45">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:32" ht="38.15" x14ac:dyDescent="0.4">
+      <c r="A46" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C46" s="17" t="s">
+      <c r="B46" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="D46" s="20" t="s">
+      <c r="C46" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="E46" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="F46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G46" s="12">
+      <c r="E46" s="12">
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="H46" s="4">
-        <v>1</v>
-      </c>
-      <c r="I46">
-        <v>2</v>
-      </c>
-      <c r="J46">
-        <v>1</v>
+      <c r="F46" s="4">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>2</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46" s="4">
+        <v>2</v>
+      </c>
+      <c r="J46" s="4">
+        <v>2</v>
       </c>
       <c r="K46" s="4">
         <v>2</v>
       </c>
       <c r="L46" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M46" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N46" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O46" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P46" s="4">
         <v>1</v>
       </c>
       <c r="Q46" s="4">
-        <v>1</v>
-      </c>
-      <c r="R46" s="4">
-        <v>1</v>
-      </c>
-      <c r="S46" s="4">
-        <v>3</v>
-      </c>
-      <c r="T46">
+        <v>3</v>
+      </c>
+      <c r="R46">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
+      <c r="S46">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="T46">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
       <c r="U46">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="V46">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="W46">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="X46" s="12">
+      <c r="V46" s="12">
         <f t="shared" si="5"/>
         <v>45</v>
       </c>
-      <c r="Y46" s="8" t="s">
+      <c r="W46" s="12"/>
+      <c r="X46" s="12">
+        <v>15</v>
+      </c>
+      <c r="Y46" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="Z46" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA46" s="17" t="s">
+      <c r="Z46" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="AB46" s="20" t="s">
+      <c r="AA46" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="AC46" s="17" t="s">
+      <c r="AB46" s="17" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="47" spans="1:30" ht="38.15" x14ac:dyDescent="0.4">
-      <c r="A47" s="8" t="s">
+      <c r="AC46" s="40"/>
+      <c r="AD46" s="37"/>
+    </row>
+    <row r="47" spans="1:32" ht="38.15" x14ac:dyDescent="0.4">
+      <c r="A47" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="B47" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" s="17" t="s">
+      <c r="B47" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="D47" s="20" t="s">
+      <c r="C47" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="E47" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G47" s="12">
+      <c r="E47" s="12">
         <f t="shared" si="4"/>
         <v>46</v>
       </c>
-      <c r="H47" s="4">
-        <v>1</v>
-      </c>
-      <c r="I47">
-        <v>2</v>
-      </c>
-      <c r="J47">
-        <v>1</v>
+      <c r="F47" s="4">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>2</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47" s="4">
+        <v>2</v>
+      </c>
+      <c r="J47" s="4">
+        <v>3</v>
       </c>
       <c r="K47" s="4">
         <v>2</v>
       </c>
       <c r="L47" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M47" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N47" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O47" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P47" s="4">
         <v>1</v>
       </c>
       <c r="Q47" s="4">
-        <v>1</v>
-      </c>
-      <c r="R47" s="4">
-        <v>1</v>
-      </c>
-      <c r="S47" s="4">
-        <v>3</v>
-      </c>
-      <c r="T47">
+        <v>3</v>
+      </c>
+      <c r="R47">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
+      <c r="S47">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="T47">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
       <c r="U47">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="V47">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="W47">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="X47" s="12">
+      <c r="V47" s="12">
         <f t="shared" si="5"/>
         <v>46</v>
       </c>
-      <c r="Y47" s="8" t="s">
+      <c r="W47" s="12"/>
+      <c r="X47" s="12">
+        <v>25</v>
+      </c>
+      <c r="Y47" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="Z47" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA47" s="17" t="s">
+      <c r="Z47" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="AB47" s="20" t="s">
+      <c r="AA47" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="AC47" s="17" t="s">
+      <c r="AB47" s="17" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="48" spans="1:30" ht="38.15" x14ac:dyDescent="0.4">
-      <c r="A48" s="8" t="s">
+      <c r="AC47" s="40"/>
+      <c r="AD47" s="37"/>
+    </row>
+    <row r="48" spans="1:32" ht="38.15" x14ac:dyDescent="0.4">
+      <c r="A48" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="B48" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="17" t="s">
+      <c r="B48" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="D48" s="20" t="s">
+      <c r="C48" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="E48" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F48" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G48" s="12">
+      <c r="E48" s="12">
         <f t="shared" si="4"/>
         <v>47</v>
       </c>
-      <c r="H48" s="4">
-        <v>2</v>
-      </c>
-      <c r="I48">
-        <v>1</v>
-      </c>
-      <c r="J48">
-        <v>2</v>
+      <c r="F48" s="4">
+        <v>2</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
+      </c>
+      <c r="I48" s="4">
+        <v>3</v>
+      </c>
+      <c r="J48" s="4">
+        <v>4</v>
       </c>
       <c r="K48" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L48" s="4">
         <v>4</v>
       </c>
       <c r="M48" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N48" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O48" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P48" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="4">
-        <v>2</v>
-      </c>
-      <c r="R48" s="4">
-        <v>1</v>
-      </c>
-      <c r="S48" s="4">
-        <v>3</v>
-      </c>
-      <c r="T48">
+        <v>3</v>
+      </c>
+      <c r="R48">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="U48">
+      <c r="S48">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="V48">
+      <c r="T48">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="W48">
+      <c r="U48">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="X48" s="12">
+      <c r="V48" s="12">
         <f t="shared" si="5"/>
         <v>47</v>
       </c>
-      <c r="Y48" s="8" t="s">
+      <c r="W48" s="12"/>
+      <c r="X48" s="12">
+        <v>23</v>
+      </c>
+      <c r="Y48" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="Z48" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA48" s="17" t="s">
+      <c r="Z48" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="AB48" s="20" t="s">
+      <c r="AA48" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="AC48" s="17" t="s">
+      <c r="AB48" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AD48">
+      <c r="AC48" s="37" t="str">
+        <f>+Z48</f>
+        <v>Sort</v>
+      </c>
+      <c r="AD48" s="37"/>
+      <c r="AE48">
         <v>40</v>
       </c>
-    </row>
-    <row r="49" spans="1:30" ht="62.15" x14ac:dyDescent="0.4">
-      <c r="A49" s="8" t="s">
+      <c r="AF48">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:32" ht="62.15" x14ac:dyDescent="0.4">
+      <c r="A49" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="B49" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="C49" s="33" t="s">
+      <c r="B49" s="33" t="s">
         <v>259</v>
       </c>
-      <c r="D49" s="34" t="s">
+      <c r="C49" s="34" t="s">
         <v>260</v>
       </c>
-      <c r="E49" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="F49" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G49" s="12">
+      <c r="E49" s="12">
         <f t="shared" si="4"/>
         <v>48</v>
       </c>
-      <c r="H49" s="4">
-        <v>3</v>
-      </c>
-      <c r="I49">
-        <v>1</v>
-      </c>
-      <c r="J49">
+      <c r="F49" s="4">
+        <v>3</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>3</v>
+      </c>
+      <c r="I49" s="4">
+        <v>3</v>
+      </c>
+      <c r="J49" s="4">
         <v>3</v>
       </c>
       <c r="K49" s="4">
         <v>3</v>
       </c>
       <c r="L49" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M49" s="4">
         <v>3</v>
       </c>
       <c r="N49" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O49" s="4">
         <v>3</v>
       </c>
       <c r="P49" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q49" s="4">
         <v>3</v>
       </c>
-      <c r="R49" s="4">
-        <v>3</v>
-      </c>
-      <c r="S49" s="4">
-        <v>3</v>
+      <c r="R49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S49">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="T49">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="U49">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="V49">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="W49">
+      <c r="U49">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="X49" s="12">
+      <c r="V49" s="12">
         <f t="shared" si="5"/>
         <v>48</v>
       </c>
-      <c r="Y49" s="8" t="s">
+      <c r="W49" s="12"/>
+      <c r="X49" s="12">
+        <v>53</v>
+      </c>
+      <c r="Y49" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="Z49" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA49" s="33" t="s">
+      <c r="Z49" s="33" t="s">
         <v>259</v>
       </c>
-      <c r="AB49" s="34" t="s">
+      <c r="AA49" s="34" t="s">
         <v>260</v>
       </c>
-      <c r="AC49" s="19" t="s">
+      <c r="AB49" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="AD49">
+      <c r="AC49" s="5" t="str">
+        <f>+Z49</f>
+        <v>Import Data</v>
+      </c>
+      <c r="AD49" s="5"/>
+      <c r="AE49">
         <v>41</v>
       </c>
-    </row>
-    <row r="50" spans="1:30" ht="37.299999999999997" x14ac:dyDescent="0.4">
-      <c r="A50" s="8" t="s">
+      <c r="AF49">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" spans="1:32" ht="37.299999999999997" x14ac:dyDescent="0.4">
+      <c r="A50" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="B50" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="C50" s="19" t="s">
+      <c r="B50" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="D50" s="34" t="s">
+      <c r="C50" s="34" t="s">
         <v>261</v>
       </c>
-      <c r="E50" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="F50" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G50" s="12">
+      <c r="E50" s="12">
         <f t="shared" si="4"/>
         <v>49</v>
       </c>
-      <c r="H50" s="4">
-        <v>4</v>
-      </c>
-      <c r="I50">
-        <v>1</v>
-      </c>
-      <c r="J50">
-        <v>3</v>
+      <c r="F50" s="4">
+        <v>4</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>3</v>
+      </c>
+      <c r="I50" s="4">
+        <v>3</v>
+      </c>
+      <c r="J50" s="4">
+        <v>2</v>
       </c>
       <c r="K50" s="4">
         <v>3</v>
@@ -8988,162 +9143,162 @@
         <v>2</v>
       </c>
       <c r="M50" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N50" s="4">
         <v>2</v>
       </c>
       <c r="O50" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P50" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q50" s="4">
-        <v>3</v>
-      </c>
-      <c r="R50" s="4">
-        <v>4</v>
-      </c>
-      <c r="S50" s="4">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="R50">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="S50">
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="T50">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="U50">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="V50">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="W50">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="X50" s="12">
+      <c r="V50" s="12">
         <f t="shared" si="5"/>
         <v>49</v>
       </c>
-      <c r="Y50" s="8" t="s">
+      <c r="W50" s="12"/>
+      <c r="X50" s="12">
+        <v>11</v>
+      </c>
+      <c r="Y50" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="Z50" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA50" s="19" t="s">
+      <c r="Z50" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="AB50" s="34" t="s">
+      <c r="AA50" s="34" t="s">
         <v>261</v>
       </c>
-      <c r="AC50" s="19" t="s">
+      <c r="AB50" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="AD50">
+      <c r="AC50" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="AD50" s="5"/>
+      <c r="AE50">
         <v>42</v>
       </c>
-    </row>
-    <row r="51" spans="1:30" ht="62.15" x14ac:dyDescent="0.4">
-      <c r="A51" s="8" t="s">
+      <c r="AF50">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:32" ht="62.15" x14ac:dyDescent="0.4">
+      <c r="A51" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="C51" s="19" t="s">
+      <c r="B51" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="D51" s="34" t="s">
+      <c r="C51" s="34" t="s">
         <v>263</v>
       </c>
-      <c r="E51" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="F51" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G51" s="12">
+      <c r="E51" s="12">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="H51" s="4">
-        <v>4</v>
-      </c>
-      <c r="I51">
-        <v>1</v>
-      </c>
-      <c r="J51">
-        <v>3</v>
+      <c r="F51" s="4">
+        <v>4</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51">
+        <v>3</v>
+      </c>
+      <c r="I51" s="4">
+        <v>3</v>
+      </c>
+      <c r="J51" s="4">
+        <v>4</v>
       </c>
       <c r="K51" s="4">
         <v>3</v>
       </c>
       <c r="L51" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M51" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N51" s="4">
         <v>2</v>
       </c>
       <c r="O51" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P51" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q51" s="4">
-        <v>3</v>
-      </c>
-      <c r="R51" s="4">
-        <v>4</v>
-      </c>
-      <c r="S51" s="4">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="R51">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="S51">
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="T51">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="U51">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="V51">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="W51">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="X51" s="12">
+      <c r="V51" s="12">
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="Y51" s="8" t="s">
+      <c r="W51" s="12"/>
+      <c r="X51" s="12">
+        <v>7</v>
+      </c>
+      <c r="Y51" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="Z51" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA51" s="19" t="s">
+      <c r="Z51" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="AB51" s="34" t="s">
+      <c r="AA51" s="34" t="s">
         <v>263</v>
       </c>
-      <c r="AC51" s="19" t="s">
+      <c r="AB51" s="19" t="s">
         <v>57</v>
       </c>
+      <c r="AC51" s="6"/>
+      <c r="AD51" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>